--- a/src/LGBM_Regressor/Master_Results.xlsx
+++ b/src/LGBM_Regressor/Master_Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\lukehunker\ELEC49X_Group53_AIweightlift\src\LGBM_Regressor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajmal\Documents\ELEC49X_Group53_AIweightlift\src\LGBM_Regressor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD8DF06-751F-4DD1-AB9F-F7B0A7375790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D26FF0-F345-4AA2-8BAB-CBBEB1432388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1965" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2666,15 +2666,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2978,20 +2975,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y774"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" customWidth="1"/>
-    <col min="9" max="9" width="16.6640625" customWidth="1"/>
-    <col min="10" max="10" width="15.33203125" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" customWidth="1"/>
-    <col min="23" max="23" width="21.44140625" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" hidden="1" customWidth="1"/>
+    <col min="13" max="22" width="12.140625" customWidth="1"/>
+    <col min="23" max="23" width="21.140625" customWidth="1"/>
+    <col min="24" max="24" width="10.5703125" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3068,7 +3071,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -3142,7 +3145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -3216,7 +3219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -3293,7 +3296,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -3370,7 +3373,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -3447,7 +3450,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -3524,7 +3527,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -3598,7 +3601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -3675,7 +3678,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -3752,7 +3755,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -3829,7 +3832,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -3903,7 +3906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -3980,7 +3983,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -4057,7 +4060,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -4134,7 +4137,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -4211,7 +4214,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -4288,7 +4291,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -4365,7 +4368,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -4439,7 +4442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -4516,7 +4519,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -4593,7 +4596,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -4667,7 +4670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -4741,7 +4744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -4815,7 +4818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -4889,7 +4892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -4963,7 +4966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -5037,7 +5040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -5114,7 +5117,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -5191,7 +5194,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -5265,7 +5268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -5339,7 +5342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -5413,7 +5416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -5487,7 +5490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -5561,7 +5564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -5638,7 +5641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>65</v>
       </c>
@@ -5715,7 +5718,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>66</v>
       </c>
@@ -5792,7 +5795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>67</v>
       </c>
@@ -5869,7 +5872,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>69</v>
       </c>
@@ -5946,7 +5949,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>71</v>
       </c>
@@ -6020,7 +6023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>72</v>
       </c>
@@ -6094,7 +6097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>73</v>
       </c>
@@ -6168,7 +6171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -6245,7 +6248,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>75</v>
       </c>
@@ -6322,7 +6325,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>76</v>
       </c>
@@ -6399,7 +6402,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>77</v>
       </c>
@@ -6476,7 +6479,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>78</v>
       </c>
@@ -6553,7 +6556,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>79</v>
       </c>
@@ -6630,7 +6633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>80</v>
       </c>
@@ -6704,7 +6707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>81</v>
       </c>
@@ -6781,7 +6784,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>82</v>
       </c>
@@ -6858,7 +6861,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>83</v>
       </c>
@@ -6935,7 +6938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>84</v>
       </c>
@@ -7012,7 +7015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>85</v>
       </c>
@@ -7086,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>86</v>
       </c>
@@ -7163,7 +7166,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>87</v>
       </c>
@@ -7240,7 +7243,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>88</v>
       </c>
@@ -7317,7 +7320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>89</v>
       </c>
@@ -7394,7 +7397,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -7471,7 +7474,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>91</v>
       </c>
@@ -7545,7 +7548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>92</v>
       </c>
@@ -7622,7 +7625,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>93</v>
       </c>
@@ -7699,7 +7702,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>94</v>
       </c>
@@ -7776,7 +7779,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>95</v>
       </c>
@@ -7853,7 +7856,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>96</v>
       </c>
@@ -7930,7 +7933,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>97</v>
       </c>
@@ -8007,7 +8010,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>98</v>
       </c>
@@ -8084,7 +8087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>99</v>
       </c>
@@ -8161,7 +8164,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>100</v>
       </c>
@@ -8235,7 +8238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>101</v>
       </c>
@@ -8312,7 +8315,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>102</v>
       </c>
@@ -8386,7 +8389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>103</v>
       </c>
@@ -8460,7 +8463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>104</v>
       </c>
@@ -8537,7 +8540,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>105</v>
       </c>
@@ -8611,7 +8614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>106</v>
       </c>
@@ -8685,7 +8688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>107</v>
       </c>
@@ -8759,7 +8762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>108</v>
       </c>
@@ -8833,7 +8836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>109</v>
       </c>
@@ -8910,7 +8913,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>110</v>
       </c>
@@ -8984,7 +8987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>111</v>
       </c>
@@ -9058,7 +9061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>112</v>
       </c>
@@ -9135,7 +9138,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>113</v>
       </c>
@@ -9212,7 +9215,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>114</v>
       </c>
@@ -9289,7 +9292,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>115</v>
       </c>
@@ -9366,7 +9369,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>116</v>
       </c>
@@ -9440,7 +9443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>117</v>
       </c>
@@ -9517,7 +9520,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>118</v>
       </c>
@@ -9594,7 +9597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>119</v>
       </c>
@@ -9668,7 +9671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>120</v>
       </c>
@@ -9745,7 +9748,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>121</v>
       </c>
@@ -9822,7 +9825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>122</v>
       </c>
@@ -9899,7 +9902,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>123</v>
       </c>
@@ -9976,7 +9979,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>124</v>
       </c>
@@ -10050,7 +10053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>125</v>
       </c>
@@ -10124,7 +10127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>126</v>
       </c>
@@ -10198,7 +10201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>127</v>
       </c>
@@ -10275,7 +10278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>128</v>
       </c>
@@ -10352,7 +10355,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>129</v>
       </c>
@@ -10429,7 +10432,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>130</v>
       </c>
@@ -10506,7 +10509,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>131</v>
       </c>
@@ -10583,7 +10586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>132</v>
       </c>
@@ -10660,7 +10663,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>133</v>
       </c>
@@ -10734,7 +10737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>134</v>
       </c>
@@ -10808,7 +10811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>135</v>
       </c>
@@ -10882,7 +10885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>136</v>
       </c>
@@ -10956,7 +10959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>137</v>
       </c>
@@ -11033,7 +11036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>138</v>
       </c>
@@ -11107,7 +11110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>139</v>
       </c>
@@ -11184,7 +11187,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>140</v>
       </c>
@@ -11261,7 +11264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>141</v>
       </c>
@@ -11338,7 +11341,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>142</v>
       </c>
@@ -11415,7 +11418,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>143</v>
       </c>
@@ -11492,7 +11495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>144</v>
       </c>
@@ -11569,7 +11572,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>145</v>
       </c>
@@ -11646,7 +11649,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>146</v>
       </c>
@@ -11723,7 +11726,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>147</v>
       </c>
@@ -11800,7 +11803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>148</v>
       </c>
@@ -11874,7 +11877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>149</v>
       </c>
@@ -11948,7 +11951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>150</v>
       </c>
@@ -12022,7 +12025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>151</v>
       </c>
@@ -12099,7 +12102,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>152</v>
       </c>
@@ -12176,7 +12179,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>153</v>
       </c>
@@ -12253,7 +12256,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>154</v>
       </c>
@@ -12327,7 +12330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>155</v>
       </c>
@@ -12401,7 +12404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>156</v>
       </c>
@@ -12475,7 +12478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>157</v>
       </c>
@@ -12552,7 +12555,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>158</v>
       </c>
@@ -12629,7 +12632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>159</v>
       </c>
@@ -12703,7 +12706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>160</v>
       </c>
@@ -12777,7 +12780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>161</v>
       </c>
@@ -12851,7 +12854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>162</v>
       </c>
@@ -12925,7 +12928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>163</v>
       </c>
@@ -12999,7 +13002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>164</v>
       </c>
@@ -13073,7 +13076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>165</v>
       </c>
@@ -13150,7 +13153,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>166</v>
       </c>
@@ -13227,7 +13230,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>167</v>
       </c>
@@ -13301,7 +13304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>168</v>
       </c>
@@ -13378,7 +13381,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>169</v>
       </c>
@@ -13455,7 +13458,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>170</v>
       </c>
@@ -13532,7 +13535,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>171</v>
       </c>
@@ -13606,7 +13609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>172</v>
       </c>
@@ -13683,7 +13686,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>173</v>
       </c>
@@ -13757,7 +13760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>174</v>
       </c>
@@ -13834,7 +13837,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>175</v>
       </c>
@@ -13908,7 +13911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>176</v>
       </c>
@@ -13985,7 +13988,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>177</v>
       </c>
@@ -14062,7 +14065,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>178</v>
       </c>
@@ -14139,7 +14142,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>179</v>
       </c>
@@ -14216,7 +14219,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>180</v>
       </c>
@@ -14293,7 +14296,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>181</v>
       </c>
@@ -14370,7 +14373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>182</v>
       </c>
@@ -14447,7 +14450,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>183</v>
       </c>
@@ -14524,7 +14527,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>184</v>
       </c>
@@ -14601,7 +14604,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>185</v>
       </c>
@@ -14678,7 +14681,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>186</v>
       </c>
@@ -14755,7 +14758,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>187</v>
       </c>
@@ -14832,7 +14835,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>188</v>
       </c>
@@ -14909,7 +14912,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>189</v>
       </c>
@@ -14986,7 +14989,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>190</v>
       </c>
@@ -15063,7 +15066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>191</v>
       </c>
@@ -15137,7 +15140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>192</v>
       </c>
@@ -15214,7 +15217,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>193</v>
       </c>
@@ -15291,7 +15294,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>194</v>
       </c>
@@ -15368,7 +15371,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>195</v>
       </c>
@@ -15445,7 +15448,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>196</v>
       </c>
@@ -15522,7 +15525,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>197</v>
       </c>
@@ -15599,7 +15602,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>198</v>
       </c>
@@ -15676,7 +15679,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>199</v>
       </c>
@@ -15753,7 +15756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>200</v>
       </c>
@@ -15827,7 +15830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>201</v>
       </c>
@@ -15901,7 +15904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>202</v>
       </c>
@@ -15945,7 +15948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>203</v>
       </c>
@@ -16019,7 +16022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>204</v>
       </c>
@@ -16093,7 +16096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>205</v>
       </c>
@@ -16167,7 +16170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>206</v>
       </c>
@@ -16244,7 +16247,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>207</v>
       </c>
@@ -16318,7 +16321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>208</v>
       </c>
@@ -16395,7 +16398,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>209</v>
       </c>
@@ -16472,7 +16475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>210</v>
       </c>
@@ -16549,7 +16552,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>211</v>
       </c>
@@ -16626,7 +16629,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>212</v>
       </c>
@@ -16703,7 +16706,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>213</v>
       </c>
@@ -16780,7 +16783,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>214</v>
       </c>
@@ -16857,7 +16860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>215</v>
       </c>
@@ -16934,7 +16937,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>216</v>
       </c>
@@ -17011,7 +17014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>217</v>
       </c>
@@ -17085,7 +17088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>218</v>
       </c>
@@ -17162,7 +17165,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>219</v>
       </c>
@@ -17236,7 +17239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>220</v>
       </c>
@@ -17310,7 +17313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>221</v>
       </c>
@@ -17384,7 +17387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>222</v>
       </c>
@@ -17461,7 +17464,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>223</v>
       </c>
@@ -17538,7 +17541,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>224</v>
       </c>
@@ -17615,7 +17618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>225</v>
       </c>
@@ -17692,7 +17695,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>226</v>
       </c>
@@ -17769,7 +17772,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>227</v>
       </c>
@@ -17846,7 +17849,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>228</v>
       </c>
@@ -17923,7 +17926,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>229</v>
       </c>
@@ -18000,7 +18003,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>230</v>
       </c>
@@ -18077,7 +18080,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>231</v>
       </c>
@@ -18154,7 +18157,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>232</v>
       </c>
@@ -18231,7 +18234,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>233</v>
       </c>
@@ -18305,7 +18308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>234</v>
       </c>
@@ -18382,7 +18385,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>235</v>
       </c>
@@ -18459,7 +18462,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>236</v>
       </c>
@@ -18536,7 +18539,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>237</v>
       </c>
@@ -18613,7 +18616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>238</v>
       </c>
@@ -18687,7 +18690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>239</v>
       </c>
@@ -18761,7 +18764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>240</v>
       </c>
@@ -18835,7 +18838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>241</v>
       </c>
@@ -18909,7 +18912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>242</v>
       </c>
@@ -18986,7 +18989,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>244</v>
       </c>
@@ -19063,7 +19066,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>245</v>
       </c>
@@ -19140,7 +19143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>246</v>
       </c>
@@ -19217,7 +19220,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>247</v>
       </c>
@@ -19294,7 +19297,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>248</v>
       </c>
@@ -19371,7 +19374,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>249</v>
       </c>
@@ -19448,7 +19451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>250</v>
       </c>
@@ -19525,7 +19528,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>251</v>
       </c>
@@ -19602,7 +19605,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>252</v>
       </c>
@@ -19679,7 +19682,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>253</v>
       </c>
@@ -19756,7 +19759,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>254</v>
       </c>
@@ -19833,7 +19836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>255</v>
       </c>
@@ -19910,7 +19913,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>256</v>
       </c>
@@ -19987,7 +19990,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="225" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>257</v>
       </c>
@@ -20031,7 +20034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>258</v>
       </c>
@@ -20105,7 +20108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>259</v>
       </c>
@@ -20179,7 +20182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>260</v>
       </c>
@@ -20253,7 +20256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>261</v>
       </c>
@@ -20327,7 +20330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>262</v>
       </c>
@@ -20401,7 +20404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>263</v>
       </c>
@@ -20475,7 +20478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>264</v>
       </c>
@@ -20549,7 +20552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>265</v>
       </c>
@@ -20623,7 +20626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>266</v>
       </c>
@@ -20697,7 +20700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>267</v>
       </c>
@@ -20771,7 +20774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>268</v>
       </c>
@@ -20845,7 +20848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>269</v>
       </c>
@@ -20919,7 +20922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>270</v>
       </c>
@@ -20993,7 +20996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>271</v>
       </c>
@@ -21067,7 +21070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>272</v>
       </c>
@@ -21141,7 +21144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>273</v>
       </c>
@@ -21215,7 +21218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>274</v>
       </c>
@@ -21289,7 +21292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>275</v>
       </c>
@@ -21363,7 +21366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>276</v>
       </c>
@@ -21437,7 +21440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>277</v>
       </c>
@@ -21511,7 +21514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>278</v>
       </c>
@@ -21585,7 +21588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>279</v>
       </c>
@@ -21659,7 +21662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>280</v>
       </c>
@@ -21733,7 +21736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>281</v>
       </c>
@@ -21807,7 +21810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>282</v>
       </c>
@@ -21881,7 +21884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>283</v>
       </c>
@@ -21955,7 +21958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>284</v>
       </c>
@@ -22029,7 +22032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>285</v>
       </c>
@@ -22103,7 +22106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>286</v>
       </c>
@@ -22177,7 +22180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>287</v>
       </c>
@@ -22251,7 +22254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>288</v>
       </c>
@@ -22325,7 +22328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>289</v>
       </c>
@@ -22399,7 +22402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>290</v>
       </c>
@@ -22473,7 +22476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>291</v>
       </c>
@@ -22547,7 +22550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>292</v>
       </c>
@@ -22621,7 +22624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>293</v>
       </c>
@@ -22695,7 +22698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>294</v>
       </c>
@@ -22769,7 +22772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>295</v>
       </c>
@@ -22843,7 +22846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>296</v>
       </c>
@@ -22917,7 +22920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>297</v>
       </c>
@@ -22991,7 +22994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>298</v>
       </c>
@@ -23065,7 +23068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>299</v>
       </c>
@@ -23139,7 +23142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>300</v>
       </c>
@@ -23213,7 +23216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>301</v>
       </c>
@@ -23287,7 +23290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>302</v>
       </c>
@@ -23361,7 +23364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>303</v>
       </c>
@@ -23438,7 +23441,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>305</v>
       </c>
@@ -23512,7 +23515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>306</v>
       </c>
@@ -23586,7 +23589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>307</v>
       </c>
@@ -23660,7 +23663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>308</v>
       </c>
@@ -23734,7 +23737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>309</v>
       </c>
@@ -23808,7 +23811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>310</v>
       </c>
@@ -23882,7 +23885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>311</v>
       </c>
@@ -23956,7 +23959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>312</v>
       </c>
@@ -24030,7 +24033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>313</v>
       </c>
@@ -24104,7 +24107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>314</v>
       </c>
@@ -24178,7 +24181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>315</v>
       </c>
@@ -24252,7 +24255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>316</v>
       </c>
@@ -24326,7 +24329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>317</v>
       </c>
@@ -24400,7 +24403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>318</v>
       </c>
@@ -24474,7 +24477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>319</v>
       </c>
@@ -24548,7 +24551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>320</v>
       </c>
@@ -24622,7 +24625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>321</v>
       </c>
@@ -24696,7 +24699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>322</v>
       </c>
@@ -24773,7 +24776,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>324</v>
       </c>
@@ -24847,7 +24850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>325</v>
       </c>
@@ -24921,7 +24924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>326</v>
       </c>
@@ -24995,7 +24998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>327</v>
       </c>
@@ -25069,7 +25072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>328</v>
       </c>
@@ -25143,7 +25146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>329</v>
       </c>
@@ -25217,7 +25220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>330</v>
       </c>
@@ -25291,7 +25294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>331</v>
       </c>
@@ -25365,7 +25368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>332</v>
       </c>
@@ -25439,7 +25442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>333</v>
       </c>
@@ -25513,7 +25516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>334</v>
       </c>
@@ -25587,7 +25590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>335</v>
       </c>
@@ -25661,7 +25664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>336</v>
       </c>
@@ -25735,7 +25738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>337</v>
       </c>
@@ -25809,7 +25812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>338</v>
       </c>
@@ -25883,7 +25886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>339</v>
       </c>
@@ -25957,7 +25960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>340</v>
       </c>
@@ -26031,7 +26034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>341</v>
       </c>
@@ -26105,7 +26108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>342</v>
       </c>
@@ -26179,7 +26182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>343</v>
       </c>
@@ -26253,7 +26256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>344</v>
       </c>
@@ -26327,7 +26330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>345</v>
       </c>
@@ -26401,7 +26404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>346</v>
       </c>
@@ -26475,7 +26478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>347</v>
       </c>
@@ -26549,7 +26552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>348</v>
       </c>
@@ -26623,7 +26626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>349</v>
       </c>
@@ -26697,7 +26700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>350</v>
       </c>
@@ -26771,7 +26774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>351</v>
       </c>
@@ -26845,7 +26848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>352</v>
       </c>
@@ -26919,7 +26922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>353</v>
       </c>
@@ -26993,7 +26996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>354</v>
       </c>
@@ -27067,7 +27070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>355</v>
       </c>
@@ -27141,7 +27144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>356</v>
       </c>
@@ -27215,7 +27218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>357</v>
       </c>
@@ -27289,7 +27292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>358</v>
       </c>
@@ -27363,7 +27366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>359</v>
       </c>
@@ -27437,7 +27440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>360</v>
       </c>
@@ -27511,7 +27514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>361</v>
       </c>
@@ -27585,7 +27588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>362</v>
       </c>
@@ -27659,7 +27662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>363</v>
       </c>
@@ -27733,7 +27736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>364</v>
       </c>
@@ -27807,7 +27810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>365</v>
       </c>
@@ -27881,7 +27884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>366</v>
       </c>
@@ -27955,7 +27958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>367</v>
       </c>
@@ -28029,7 +28032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>368</v>
       </c>
@@ -28106,7 +28109,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>370</v>
       </c>
@@ -28183,7 +28186,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>371</v>
       </c>
@@ -28260,7 +28263,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>372</v>
       </c>
@@ -28337,7 +28340,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>374</v>
       </c>
@@ -28414,7 +28417,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>375</v>
       </c>
@@ -28488,7 +28491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>376</v>
       </c>
@@ -28562,7 +28565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>377</v>
       </c>
@@ -28636,7 +28639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>378</v>
       </c>
@@ -28710,7 +28713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>379</v>
       </c>
@@ -28784,7 +28787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>380</v>
       </c>
@@ -28858,7 +28861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>381</v>
       </c>
@@ -28932,7 +28935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>382</v>
       </c>
@@ -29006,7 +29009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>383</v>
       </c>
@@ -29080,7 +29083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>384</v>
       </c>
@@ -29154,7 +29157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>385</v>
       </c>
@@ -29231,7 +29234,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>386</v>
       </c>
@@ -29308,7 +29311,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>387</v>
       </c>
@@ -29385,7 +29388,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>389</v>
       </c>
@@ -29462,7 +29465,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="353" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>390</v>
       </c>
@@ -29539,7 +29542,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>391</v>
       </c>
@@ -29616,7 +29619,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="355" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>392</v>
       </c>
@@ -29693,7 +29696,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>394</v>
       </c>
@@ -29770,7 +29773,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>395</v>
       </c>
@@ -29847,7 +29850,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>396</v>
       </c>
@@ -29921,7 +29924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>397</v>
       </c>
@@ -29995,7 +29998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>398</v>
       </c>
@@ -30069,7 +30072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>399</v>
       </c>
@@ -30143,7 +30146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>400</v>
       </c>
@@ -30217,7 +30220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>401</v>
       </c>
@@ -30294,7 +30297,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>402</v>
       </c>
@@ -30368,7 +30371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>403</v>
       </c>
@@ -30442,7 +30445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>404</v>
       </c>
@@ -30516,7 +30519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>405</v>
       </c>
@@ -30590,7 +30593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>406</v>
       </c>
@@ -30664,7 +30667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>407</v>
       </c>
@@ -30741,7 +30744,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>408</v>
       </c>
@@ -30818,7 +30821,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>409</v>
       </c>
@@ -30895,7 +30898,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>410</v>
       </c>
@@ -30972,7 +30975,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>411</v>
       </c>
@@ -31049,7 +31052,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>412</v>
       </c>
@@ -31123,7 +31126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>413</v>
       </c>
@@ -31197,7 +31200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>414</v>
       </c>
@@ -31271,7 +31274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>415</v>
       </c>
@@ -31348,7 +31351,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>416</v>
       </c>
@@ -31422,7 +31425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>417</v>
       </c>
@@ -31496,7 +31499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>418</v>
       </c>
@@ -31567,7 +31570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>419</v>
       </c>
@@ -31641,7 +31644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>420</v>
       </c>
@@ -31712,7 +31715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>421</v>
       </c>
@@ -31786,7 +31789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>422</v>
       </c>
@@ -31860,7 +31863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>423</v>
       </c>
@@ -31934,7 +31937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>424</v>
       </c>
@@ -32011,7 +32014,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>425</v>
       </c>
@@ -32088,7 +32091,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>426</v>
       </c>
@@ -32165,7 +32168,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>427</v>
       </c>
@@ -32239,7 +32242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>428</v>
       </c>
@@ -32313,7 +32316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>429</v>
       </c>
@@ -32387,7 +32390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>430</v>
       </c>
@@ -32461,7 +32464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>431</v>
       </c>
@@ -32535,7 +32538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>432</v>
       </c>
@@ -32609,7 +32612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>433</v>
       </c>
@@ -32683,7 +32686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>434</v>
       </c>
@@ -32757,7 +32760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>435</v>
       </c>
@@ -32831,7 +32834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>436</v>
       </c>
@@ -32905,7 +32908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>437</v>
       </c>
@@ -32979,7 +32982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>438</v>
       </c>
@@ -33053,7 +33056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>439</v>
       </c>
@@ -33127,7 +33130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>440</v>
       </c>
@@ -33201,7 +33204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>441</v>
       </c>
@@ -33275,7 +33278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>442</v>
       </c>
@@ -33349,7 +33352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>443</v>
       </c>
@@ -33423,7 +33426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>444</v>
       </c>
@@ -33497,7 +33500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>445</v>
       </c>
@@ -33571,7 +33574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>446</v>
       </c>
@@ -33645,7 +33648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>447</v>
       </c>
@@ -33719,7 +33722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>448</v>
       </c>
@@ -33793,7 +33796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>449</v>
       </c>
@@ -33867,7 +33870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>450</v>
       </c>
@@ -33941,7 +33944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>451</v>
       </c>
@@ -34015,7 +34018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>452</v>
       </c>
@@ -34089,7 +34092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>453</v>
       </c>
@@ -34163,7 +34166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>454</v>
       </c>
@@ -34237,7 +34240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>455</v>
       </c>
@@ -34311,7 +34314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>456</v>
       </c>
@@ -34385,7 +34388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>457</v>
       </c>
@@ -34459,7 +34462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>458</v>
       </c>
@@ -34533,7 +34536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>459</v>
       </c>
@@ -34607,7 +34610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>460</v>
       </c>
@@ -34684,7 +34687,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>461</v>
       </c>
@@ -34758,7 +34761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>462</v>
       </c>
@@ -34832,7 +34835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>463</v>
       </c>
@@ -34906,7 +34909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>464</v>
       </c>
@@ -34980,7 +34983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>465</v>
       </c>
@@ -35054,7 +35057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>466</v>
       </c>
@@ -35128,7 +35131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>467</v>
       </c>
@@ -35202,7 +35205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>468</v>
       </c>
@@ -35279,7 +35282,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>469</v>
       </c>
@@ -35356,7 +35359,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>470</v>
       </c>
@@ -35430,7 +35433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>471</v>
       </c>
@@ -35504,7 +35507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>472</v>
       </c>
@@ -35578,7 +35581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>473</v>
       </c>
@@ -35652,7 +35655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>474</v>
       </c>
@@ -35726,7 +35729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>475</v>
       </c>
@@ -35800,7 +35803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>476</v>
       </c>
@@ -35874,7 +35877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>477</v>
       </c>
@@ -35948,7 +35951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>478</v>
       </c>
@@ -36022,7 +36025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>479</v>
       </c>
@@ -36096,7 +36099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>480</v>
       </c>
@@ -36170,7 +36173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>481</v>
       </c>
@@ -36244,7 +36247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>482</v>
       </c>
@@ -36318,7 +36321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>483</v>
       </c>
@@ -36395,7 +36398,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>485</v>
       </c>
@@ -36472,7 +36475,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>486</v>
       </c>
@@ -36546,7 +36549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>487</v>
       </c>
@@ -36620,7 +36623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>488</v>
       </c>
@@ -36694,7 +36697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>489</v>
       </c>
@@ -36768,7 +36771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>490</v>
       </c>
@@ -36845,7 +36848,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>492</v>
       </c>
@@ -36922,7 +36925,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>494</v>
       </c>
@@ -36996,7 +36999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>495</v>
       </c>
@@ -37070,7 +37073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>496</v>
       </c>
@@ -37144,7 +37147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>497</v>
       </c>
@@ -37218,7 +37221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>498</v>
       </c>
@@ -37292,7 +37295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>499</v>
       </c>
@@ -37366,7 +37369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>500</v>
       </c>
@@ -37440,7 +37443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>501</v>
       </c>
@@ -37514,7 +37517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>502</v>
       </c>
@@ -37588,7 +37591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>503</v>
       </c>
@@ -37665,7 +37668,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>504</v>
       </c>
@@ -37742,7 +37745,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>506</v>
       </c>
@@ -37819,7 +37822,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>508</v>
       </c>
@@ -37896,7 +37899,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>509</v>
       </c>
@@ -37973,7 +37976,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>510</v>
       </c>
@@ -38047,7 +38050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>511</v>
       </c>
@@ -38121,7 +38124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>512</v>
       </c>
@@ -38195,7 +38198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>513</v>
       </c>
@@ -38269,7 +38272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>514</v>
       </c>
@@ -38343,7 +38346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>515</v>
       </c>
@@ -38417,7 +38420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>516</v>
       </c>
@@ -38494,7 +38497,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>517</v>
       </c>
@@ -38568,7 +38571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>518</v>
       </c>
@@ -38642,7 +38645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>519</v>
       </c>
@@ -38716,7 +38719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>520</v>
       </c>
@@ -38790,7 +38793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>521</v>
       </c>
@@ -38864,7 +38867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>522</v>
       </c>
@@ -38938,7 +38941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>523</v>
       </c>
@@ -39012,7 +39015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>524</v>
       </c>
@@ -39086,7 +39089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>525</v>
       </c>
@@ -39160,7 +39163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>526</v>
       </c>
@@ -39234,7 +39237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>527</v>
       </c>
@@ -39308,7 +39311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>528</v>
       </c>
@@ -39382,7 +39385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>529</v>
       </c>
@@ -39456,7 +39459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>530</v>
       </c>
@@ -39530,7 +39533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>531</v>
       </c>
@@ -39604,7 +39607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>532</v>
       </c>
@@ -39678,7 +39681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>533</v>
       </c>
@@ -39752,7 +39755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>534</v>
       </c>
@@ -39826,7 +39829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>535</v>
       </c>
@@ -39900,7 +39903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>536</v>
       </c>
@@ -39974,7 +39977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>537</v>
       </c>
@@ -40048,7 +40051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>538</v>
       </c>
@@ -40122,7 +40125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>539</v>
       </c>
@@ -40196,7 +40199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>540</v>
       </c>
@@ -40270,7 +40273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>541</v>
       </c>
@@ -40344,7 +40347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>542</v>
       </c>
@@ -40418,7 +40421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>543</v>
       </c>
@@ -40492,7 +40495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>544</v>
       </c>
@@ -40566,7 +40569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>545</v>
       </c>
@@ -40640,7 +40643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>546</v>
       </c>
@@ -40717,7 +40720,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>547</v>
       </c>
@@ -40794,7 +40797,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>548</v>
       </c>
@@ -40871,7 +40874,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>549</v>
       </c>
@@ -40948,7 +40951,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>550</v>
       </c>
@@ -41025,7 +41028,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>551</v>
       </c>
@@ -41099,7 +41102,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>552</v>
       </c>
@@ -41176,7 +41179,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>553</v>
       </c>
@@ -41250,7 +41253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>554</v>
       </c>
@@ -41324,7 +41327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>555</v>
       </c>
@@ -41398,7 +41401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>556</v>
       </c>
@@ -41472,7 +41475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>557</v>
       </c>
@@ -41546,7 +41549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>558</v>
       </c>
@@ -41620,7 +41623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>559</v>
       </c>
@@ -41694,7 +41697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>560</v>
       </c>
@@ -41768,7 +41771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>561</v>
       </c>
@@ -41842,7 +41845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>562</v>
       </c>
@@ -41916,7 +41919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>563</v>
       </c>
@@ -41990,7 +41993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>564</v>
       </c>
@@ -42064,7 +42067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>565</v>
       </c>
@@ -42138,7 +42141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>566</v>
       </c>
@@ -42212,7 +42215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>567</v>
       </c>
@@ -42286,7 +42289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>568</v>
       </c>
@@ -42360,7 +42363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>569</v>
       </c>
@@ -42434,7 +42437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>570</v>
       </c>
@@ -42508,7 +42511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>571</v>
       </c>
@@ -42582,7 +42585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>572</v>
       </c>
@@ -42656,7 +42659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>573</v>
       </c>
@@ -42730,7 +42733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>574</v>
       </c>
@@ -42804,7 +42807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>575</v>
       </c>
@@ -42878,7 +42881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>576</v>
       </c>
@@ -42952,7 +42955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>577</v>
       </c>
@@ -43026,7 +43029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>578</v>
       </c>
@@ -43100,7 +43103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>579</v>
       </c>
@@ -43174,7 +43177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>580</v>
       </c>
@@ -43248,7 +43251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>581</v>
       </c>
@@ -43322,7 +43325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>582</v>
       </c>
@@ -43396,7 +43399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>583</v>
       </c>
@@ -43470,7 +43473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>584</v>
       </c>
@@ -43544,7 +43547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>585</v>
       </c>
@@ -43618,7 +43621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>586</v>
       </c>
@@ -43692,7 +43695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>587</v>
       </c>
@@ -43766,7 +43769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>588</v>
       </c>
@@ -43840,7 +43843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>589</v>
       </c>
@@ -43914,7 +43917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>590</v>
       </c>
@@ -43988,7 +43991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>591</v>
       </c>
@@ -44062,7 +44065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>592</v>
       </c>
@@ -44136,7 +44139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>593</v>
       </c>
@@ -44210,7 +44213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>594</v>
       </c>
@@ -44284,7 +44287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>595</v>
       </c>
@@ -44358,7 +44361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>596</v>
       </c>
@@ -44432,7 +44435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>597</v>
       </c>
@@ -44506,7 +44509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>598</v>
       </c>
@@ -44580,7 +44583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>599</v>
       </c>
@@ -44654,7 +44657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>600</v>
       </c>
@@ -44728,7 +44731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>601</v>
       </c>
@@ -44802,7 +44805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>602</v>
       </c>
@@ -44876,7 +44879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>603</v>
       </c>
@@ -44950,7 +44953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>604</v>
       </c>
@@ -45024,7 +45027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>605</v>
       </c>
@@ -45098,7 +45101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>606</v>
       </c>
@@ -45172,7 +45175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>607</v>
       </c>
@@ -45246,7 +45249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>608</v>
       </c>
@@ -45320,7 +45323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>609</v>
       </c>
@@ -45394,7 +45397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>610</v>
       </c>
@@ -45468,7 +45471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>611</v>
       </c>
@@ -45542,7 +45545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>612</v>
       </c>
@@ -45616,7 +45619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>613</v>
       </c>
@@ -45690,7 +45693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>614</v>
       </c>
@@ -45764,7 +45767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>615</v>
       </c>
@@ -45838,7 +45841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>616</v>
       </c>
@@ -45912,7 +45915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>617</v>
       </c>
@@ -45986,7 +45989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>618</v>
       </c>
@@ -46060,7 +46063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>619</v>
       </c>
@@ -46134,7 +46137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>620</v>
       </c>
@@ -46208,7 +46211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>621</v>
       </c>
@@ -46282,7 +46285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>622</v>
       </c>
@@ -46356,7 +46359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>623</v>
       </c>
@@ -46430,7 +46433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>624</v>
       </c>
@@ -46504,7 +46507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>625</v>
       </c>
@@ -46578,7 +46581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>626</v>
       </c>
@@ -46652,7 +46655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>627</v>
       </c>
@@ -46726,7 +46729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>628</v>
       </c>
@@ -46800,7 +46803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>629</v>
       </c>
@@ -46874,7 +46877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>630</v>
       </c>
@@ -46951,7 +46954,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>631</v>
       </c>
@@ -47025,7 +47028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>632</v>
       </c>
@@ -47102,7 +47105,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>634</v>
       </c>
@@ -47176,7 +47179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>635</v>
       </c>
@@ -47250,7 +47253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>636</v>
       </c>
@@ -47324,7 +47327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>637</v>
       </c>
@@ -47398,7 +47401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>638</v>
       </c>
@@ -47472,7 +47475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>639</v>
       </c>
@@ -47546,7 +47549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>640</v>
       </c>
@@ -47620,7 +47623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>641</v>
       </c>
@@ -47694,7 +47697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>642</v>
       </c>
@@ -47768,7 +47771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>643</v>
       </c>
@@ -47842,7 +47845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>644</v>
       </c>
@@ -47916,7 +47919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>645</v>
       </c>
@@ -47990,7 +47993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>646</v>
       </c>
@@ -48064,7 +48067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>647</v>
       </c>
@@ -48138,7 +48141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>648</v>
       </c>
@@ -48212,7 +48215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>649</v>
       </c>
@@ -48286,7 +48289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>650</v>
       </c>
@@ -48360,7 +48363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>651</v>
       </c>
@@ -48434,7 +48437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>652</v>
       </c>
@@ -48511,7 +48514,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>653</v>
       </c>
@@ -48585,7 +48588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>654</v>
       </c>
@@ -48662,7 +48665,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>655</v>
       </c>
@@ -48736,7 +48739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>656</v>
       </c>
@@ -48810,7 +48813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>657</v>
       </c>
@@ -48884,7 +48887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>658</v>
       </c>
@@ -48958,7 +48961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>659</v>
       </c>
@@ -49032,7 +49035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>660</v>
       </c>
@@ -49109,7 +49112,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>661</v>
       </c>
@@ -49183,7 +49186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>662</v>
       </c>
@@ -49260,7 +49263,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>663</v>
       </c>
@@ -49337,7 +49340,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>664</v>
       </c>
@@ -49411,7 +49414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>665</v>
       </c>
@@ -49485,7 +49488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>666</v>
       </c>
@@ -49562,7 +49565,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>667</v>
       </c>
@@ -49636,7 +49639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>668</v>
       </c>
@@ -49713,7 +49716,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>669</v>
       </c>
@@ -49787,7 +49790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>670</v>
       </c>
@@ -49861,7 +49864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>671</v>
       </c>
@@ -49935,7 +49938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>672</v>
       </c>
@@ -50009,7 +50012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>673</v>
       </c>
@@ -50083,7 +50086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>674</v>
       </c>
@@ -50157,7 +50160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>675</v>
       </c>
@@ -50231,7 +50234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>676</v>
       </c>
@@ -50305,7 +50308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>677</v>
       </c>
@@ -50379,7 +50382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>678</v>
       </c>
@@ -50453,7 +50456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>679</v>
       </c>
@@ -50530,7 +50533,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>680</v>
       </c>
@@ -50607,7 +50610,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>681</v>
       </c>
@@ -50684,7 +50687,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>682</v>
       </c>
@@ -50761,7 +50764,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>683</v>
       </c>
@@ -50838,7 +50841,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>684</v>
       </c>
@@ -50915,7 +50918,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>685</v>
       </c>
@@ -50992,7 +50995,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>686</v>
       </c>
@@ -51069,7 +51072,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>687</v>
       </c>
@@ -51146,7 +51149,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>688</v>
       </c>
@@ -51223,7 +51226,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>689</v>
       </c>
@@ -51297,7 +51300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>690</v>
       </c>
@@ -51374,7 +51377,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>691</v>
       </c>
@@ -51448,7 +51451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>692</v>
       </c>
@@ -51522,7 +51525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>693</v>
       </c>
@@ -51596,7 +51599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>694</v>
       </c>
@@ -51670,7 +51673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>695</v>
       </c>
@@ -51744,7 +51747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>696</v>
       </c>
@@ -51818,7 +51821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>697</v>
       </c>
@@ -51892,7 +51895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>698</v>
       </c>
@@ -51966,7 +51969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>699</v>
       </c>
@@ -52040,7 +52043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>700</v>
       </c>
@@ -52114,7 +52117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>701</v>
       </c>
@@ -52188,7 +52191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>702</v>
       </c>
@@ -52262,7 +52265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>703</v>
       </c>
@@ -52336,7 +52339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>704</v>
       </c>
@@ -52410,7 +52413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>705</v>
       </c>
@@ -52484,7 +52487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>706</v>
       </c>
@@ -52558,7 +52561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>707</v>
       </c>
@@ -52632,7 +52635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>708</v>
       </c>
@@ -52706,7 +52709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>709</v>
       </c>
@@ -52780,7 +52783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>710</v>
       </c>
@@ -52854,7 +52857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>711</v>
       </c>
@@ -52928,7 +52931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>712</v>
       </c>
@@ -53005,7 +53008,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>713</v>
       </c>
@@ -53082,7 +53085,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>714</v>
       </c>
@@ -53159,7 +53162,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>715</v>
       </c>
@@ -53233,7 +53236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>716</v>
       </c>
@@ -53307,7 +53310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>717</v>
       </c>
@@ -53381,7 +53384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>718</v>
       </c>
@@ -53455,7 +53458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>719</v>
       </c>
@@ -53529,7 +53532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>720</v>
       </c>
@@ -53603,7 +53606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>721</v>
       </c>
@@ -53677,7 +53680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>722</v>
       </c>
@@ -53751,7 +53754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>723</v>
       </c>
@@ -53825,7 +53828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>724</v>
       </c>
@@ -53899,7 +53902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>725</v>
       </c>
@@ -53973,7 +53976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>726</v>
       </c>
@@ -54047,7 +54050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="683" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>727</v>
       </c>
@@ -54121,7 +54124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>728</v>
       </c>
@@ -54195,7 +54198,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>729</v>
       </c>
@@ -54269,7 +54272,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>730</v>
       </c>
@@ -54343,7 +54346,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>731</v>
       </c>
@@ -54417,7 +54420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>732</v>
       </c>
@@ -54491,7 +54494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>733</v>
       </c>
@@ -54565,7 +54568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>734</v>
       </c>
@@ -54639,7 +54642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>735</v>
       </c>
@@ -54713,7 +54716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>736</v>
       </c>
@@ -54787,7 +54790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>737</v>
       </c>
@@ -54861,7 +54864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>738</v>
       </c>
@@ -54935,7 +54938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>739</v>
       </c>
@@ -55009,7 +55012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>740</v>
       </c>
@@ -55086,7 +55089,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="697" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>741</v>
       </c>
@@ -55160,7 +55163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="698" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>742</v>
       </c>
@@ -55234,7 +55237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="699" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>743</v>
       </c>
@@ -55311,7 +55314,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="700" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>744</v>
       </c>
@@ -55385,7 +55388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>745</v>
       </c>
@@ -55459,7 +55462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="702" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>746</v>
       </c>
@@ -55533,7 +55536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>747</v>
       </c>
@@ -55607,7 +55610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>748</v>
       </c>
@@ -55681,7 +55684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="705" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>749</v>
       </c>
@@ -55758,7 +55761,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="706" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>750</v>
       </c>
@@ -55835,7 +55838,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="707" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>751</v>
       </c>
@@ -55912,7 +55915,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="708" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>752</v>
       </c>
@@ -55986,7 +55989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="709" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>753</v>
       </c>
@@ -56060,7 +56063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>754</v>
       </c>
@@ -56134,7 +56137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="711" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>755</v>
       </c>
@@ -56208,7 +56211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="712" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>756</v>
       </c>
@@ -56282,7 +56285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>757</v>
       </c>
@@ -56356,7 +56359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="714" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>758</v>
       </c>
@@ -56430,7 +56433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>759</v>
       </c>
@@ -56504,7 +56507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>760</v>
       </c>
@@ -56578,7 +56581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>761</v>
       </c>
@@ -56652,7 +56655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>762</v>
       </c>
@@ -56726,7 +56729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="719" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>763</v>
       </c>
@@ -56800,7 +56803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="720" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>764</v>
       </c>
@@ -56874,7 +56877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="721" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>765</v>
       </c>
@@ -56948,7 +56951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="722" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>766</v>
       </c>
@@ -57022,7 +57025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>767</v>
       </c>
@@ -57096,7 +57099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="724" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>768</v>
       </c>
@@ -57173,7 +57176,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="725" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>769</v>
       </c>
@@ -57250,7 +57253,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="726" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>770</v>
       </c>
@@ -57327,7 +57330,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="727" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>771</v>
       </c>
@@ -57404,7 +57407,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="728" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>772</v>
       </c>
@@ -57481,7 +57484,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="729" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>773</v>
       </c>
@@ -57558,7 +57561,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="730" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>774</v>
       </c>
@@ -57635,7 +57638,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="731" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>775</v>
       </c>
@@ -57709,7 +57712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="732" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>776</v>
       </c>
@@ -57783,7 +57786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>777</v>
       </c>
@@ -57857,7 +57860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="734" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>778</v>
       </c>
@@ -57931,7 +57934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="735" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>779</v>
       </c>
@@ -58005,7 +58008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="736" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>780</v>
       </c>
@@ -58079,7 +58082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="737" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>781</v>
       </c>
@@ -58153,7 +58156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="738" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>782</v>
       </c>
@@ -58230,7 +58233,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="739" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>783</v>
       </c>
@@ -58307,7 +58310,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="740" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>784</v>
       </c>
@@ -58384,7 +58387,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="741" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>785</v>
       </c>
@@ -58461,7 +58464,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="742" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>786</v>
       </c>
@@ -58538,7 +58541,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="743" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>787</v>
       </c>
@@ -58615,7 +58618,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="744" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>788</v>
       </c>
@@ -58692,7 +58695,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="745" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>789</v>
       </c>
@@ -58769,7 +58772,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="746" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>790</v>
       </c>
@@ -58846,7 +58849,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="747" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>791</v>
       </c>
@@ -58923,7 +58926,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="748" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>792</v>
       </c>
@@ -58997,7 +59000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>793</v>
       </c>
@@ -59074,7 +59077,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="750" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>794</v>
       </c>
@@ -59151,7 +59154,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="751" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>795</v>
       </c>
@@ -59228,7 +59231,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="752" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>796</v>
       </c>
@@ -59305,7 +59308,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="753" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>797</v>
       </c>
@@ -59382,20 +59385,20 @@
         <v>633</v>
       </c>
     </row>
-    <row r="754" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>798</v>
       </c>
       <c r="B754">
         <v>3</v>
       </c>
-      <c r="C754" s="3">
+      <c r="C754">
         <v>8</v>
       </c>
-      <c r="D754" s="4">
+      <c r="D754">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="E754" s="5" t="b">
+      <c r="E754" t="b">
         <v>0</v>
       </c>
       <c r="F754">
@@ -59404,84 +59407,84 @@
       <c r="G754" s="2" t="s">
         <v>819</v>
       </c>
-      <c r="H754" s="5">
+      <c r="H754">
         <v>436</v>
       </c>
-      <c r="I754" s="5">
+      <c r="I754">
         <v>462</v>
       </c>
       <c r="J754" s="2" t="s">
         <v>820</v>
       </c>
-      <c r="K754" s="5">
+      <c r="K754">
         <v>4.5152815619956398E-2</v>
       </c>
-      <c r="L754" s="5">
+      <c r="L754">
         <v>0.77</v>
       </c>
-      <c r="M754" s="5">
+      <c r="M754">
         <v>2.38</v>
       </c>
-      <c r="N754" s="5">
+      <c r="N754">
         <v>0.51</v>
       </c>
-      <c r="O754" s="5">
+      <c r="O754">
         <v>2.75</v>
       </c>
-      <c r="P754" s="5">
+      <c r="P754">
         <v>1.03</v>
       </c>
-      <c r="Q754" s="5">
+      <c r="Q754">
         <v>3.04</v>
       </c>
-      <c r="R754" s="5">
+      <c r="R754">
         <v>0.56999999999999995</v>
       </c>
-      <c r="S754" s="5">
+      <c r="S754">
         <v>3.09</v>
       </c>
-      <c r="T754" s="5">
+      <c r="T754">
         <v>2.36</v>
       </c>
-      <c r="U754" s="5">
+      <c r="U754">
         <v>1.24</v>
       </c>
-      <c r="V754" s="5">
+      <c r="V754">
         <v>1.95</v>
       </c>
-      <c r="W754" s="5">
+      <c r="W754">
         <v>1</v>
       </c>
-      <c r="X754" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="755" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="X754" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="755" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>799</v>
       </c>
       <c r="B755">
         <v>3</v>
       </c>
-      <c r="C755" s="3">
+      <c r="C755">
         <v>9</v>
       </c>
-      <c r="D755" s="4">
+      <c r="D755">
         <v>-9.9999999999999978E-2</v>
       </c>
-      <c r="E755" s="5" t="b">
+      <c r="E755" t="b">
         <v>0</v>
       </c>
       <c r="F755">
         <v>0.138187676668167</v>
       </c>
-      <c r="G755" s="5">
+      <c r="G755">
         <v>0.94623655913978499</v>
       </c>
-      <c r="H755" s="5">
+      <c r="H755">
         <v>440</v>
       </c>
-      <c r="I755" s="5">
+      <c r="I755">
         <v>465</v>
       </c>
       <c r="J755" s="2" t="s">
@@ -59490,60 +59493,60 @@
       <c r="K755" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="L755" s="5">
+      <c r="L755">
         <v>0.77</v>
       </c>
-      <c r="M755" s="5">
+      <c r="M755">
         <v>2.16</v>
       </c>
-      <c r="N755" s="5">
+      <c r="N755">
         <v>1.28</v>
       </c>
-      <c r="O755" s="5">
+      <c r="O755">
         <v>3.17</v>
       </c>
-      <c r="P755" s="5">
+      <c r="P755">
         <v>1.79</v>
       </c>
-      <c r="Q755" s="5">
+      <c r="Q755">
         <v>2.2200000000000002</v>
       </c>
-      <c r="R755" s="5">
+      <c r="R755">
         <v>0.51</v>
       </c>
-      <c r="S755" s="5">
+      <c r="S755">
         <v>2.5</v>
       </c>
-      <c r="T755" s="5">
+      <c r="T755">
         <v>2.3199999999999998</v>
       </c>
-      <c r="U755" s="5">
+      <c r="U755">
         <v>2.57</v>
       </c>
-      <c r="V755" s="5">
+      <c r="V755">
         <v>1.41</v>
       </c>
-      <c r="W755" s="5">
-        <v>0</v>
-      </c>
-      <c r="X755" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="756" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W755">
+        <v>0</v>
+      </c>
+      <c r="X755" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="756" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>800</v>
       </c>
       <c r="B756">
         <v>3</v>
       </c>
-      <c r="C756" s="3">
+      <c r="C756">
         <v>8</v>
       </c>
-      <c r="D756" s="4">
+      <c r="D756">
         <v>6.6666666666666652E-2</v>
       </c>
-      <c r="E756" s="5" t="b">
+      <c r="E756" t="b">
         <v>0</v>
       </c>
       <c r="F756">
@@ -59552,72 +59555,72 @@
       <c r="G756" s="2" t="s">
         <v>823</v>
       </c>
-      <c r="H756" s="5">
+      <c r="H756">
         <v>464</v>
       </c>
-      <c r="I756" s="5">
+      <c r="I756">
         <v>483</v>
       </c>
       <c r="J756" s="2" t="s">
         <v>824</v>
       </c>
-      <c r="K756" s="5">
+      <c r="K756">
         <v>5.4731613768383501E-2</v>
       </c>
-      <c r="L756" s="5">
+      <c r="L756">
         <v>0.77</v>
       </c>
-      <c r="M756" s="5">
+      <c r="M756">
         <v>1.78</v>
       </c>
-      <c r="N756" s="5">
+      <c r="N756">
         <v>1</v>
       </c>
-      <c r="O756" s="5">
+      <c r="O756">
         <v>0.67</v>
       </c>
-      <c r="P756" s="5">
+      <c r="P756">
         <v>1.34</v>
       </c>
-      <c r="Q756" s="5">
+      <c r="Q756">
         <v>2.4500000000000002</v>
       </c>
-      <c r="R756" s="5">
+      <c r="R756">
         <v>0.7</v>
       </c>
-      <c r="S756" s="5">
+      <c r="S756">
         <v>2.06</v>
       </c>
-      <c r="T756" s="5">
+      <c r="T756">
         <v>1.82</v>
       </c>
-      <c r="U756" s="5">
+      <c r="U756">
         <v>1.65</v>
       </c>
-      <c r="V756" s="5">
+      <c r="V756">
         <v>3.54</v>
       </c>
-      <c r="W756" s="5">
-        <v>0</v>
-      </c>
-      <c r="X756" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="757" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W756">
+        <v>0</v>
+      </c>
+      <c r="X756" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="757" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>801</v>
       </c>
       <c r="B757">
         <v>3</v>
       </c>
-      <c r="C757" s="3">
+      <c r="C757">
         <v>8</v>
       </c>
-      <c r="D757" s="4">
+      <c r="D757">
         <v>-6.6666666666666652E-2</v>
       </c>
-      <c r="E757" s="5" t="b">
+      <c r="E757" t="b">
         <v>0</v>
       </c>
       <c r="F757">
@@ -59626,72 +59629,72 @@
       <c r="G757" s="2" t="s">
         <v>825</v>
       </c>
-      <c r="H757" s="5">
+      <c r="H757">
         <v>577</v>
       </c>
-      <c r="I757" s="5">
+      <c r="I757">
         <v>660</v>
       </c>
       <c r="J757" s="2" t="s">
         <v>826</v>
       </c>
-      <c r="K757" s="5">
+      <c r="K757">
         <v>5.3679849228286503E-2</v>
       </c>
-      <c r="L757" s="5">
+      <c r="L757">
         <v>0.77</v>
       </c>
-      <c r="M757" s="5">
+      <c r="M757">
         <v>2.36</v>
       </c>
-      <c r="N757" s="5">
+      <c r="N757">
         <v>1.46</v>
       </c>
-      <c r="O757" s="5">
+      <c r="O757">
         <v>2.38</v>
       </c>
-      <c r="P757" s="5">
+      <c r="P757">
         <v>1.1299999999999999</v>
       </c>
-      <c r="Q757" s="5">
+      <c r="Q757">
         <v>1.9</v>
       </c>
-      <c r="R757" s="5">
+      <c r="R757">
         <v>1.21</v>
       </c>
-      <c r="S757" s="5">
+      <c r="S757">
         <v>3.55</v>
       </c>
-      <c r="T757" s="5">
+      <c r="T757">
         <v>2.92</v>
       </c>
-      <c r="U757" s="5">
+      <c r="U757">
         <v>3.22</v>
       </c>
-      <c r="V757" s="5">
+      <c r="V757">
         <v>2.4900000000000002</v>
       </c>
-      <c r="W757" s="5">
+      <c r="W757">
         <v>1</v>
       </c>
-      <c r="X757" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="758" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="X757" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="758" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>802</v>
       </c>
       <c r="B758">
         <v>3</v>
       </c>
-      <c r="C758" s="3">
+      <c r="C758">
         <v>8</v>
       </c>
-      <c r="D758" s="4">
-        <v>0</v>
-      </c>
-      <c r="E758" s="5" t="b">
+      <c r="D758">
+        <v>0</v>
+      </c>
+      <c r="E758" t="b">
         <v>0</v>
       </c>
       <c r="F758">
@@ -59700,72 +59703,72 @@
       <c r="G758" s="2" t="s">
         <v>827</v>
       </c>
-      <c r="H758" s="5">
+      <c r="H758">
         <v>363</v>
       </c>
-      <c r="I758" s="5">
+      <c r="I758">
         <v>447</v>
       </c>
       <c r="J758" s="2" t="s">
         <v>828</v>
       </c>
-      <c r="K758" s="5">
+      <c r="K758">
         <v>6.6531692200021905E-2</v>
       </c>
-      <c r="L758" s="5">
+      <c r="L758">
         <v>0.77</v>
       </c>
-      <c r="M758" s="5">
+      <c r="M758">
         <v>2.8</v>
       </c>
-      <c r="N758" s="5">
+      <c r="N758">
         <v>0.51</v>
       </c>
-      <c r="O758" s="5">
+      <c r="O758">
         <v>1.95</v>
       </c>
-      <c r="P758" s="5">
+      <c r="P758">
         <v>0.71</v>
       </c>
-      <c r="Q758" s="5">
+      <c r="Q758">
         <v>1.24</v>
       </c>
-      <c r="R758" s="5">
+      <c r="R758">
         <v>0.84</v>
       </c>
-      <c r="S758" s="5">
+      <c r="S758">
         <v>3.04</v>
       </c>
-      <c r="T758" s="5">
+      <c r="T758">
         <v>1.77</v>
       </c>
-      <c r="U758" s="5">
+      <c r="U758">
         <v>1.96</v>
       </c>
-      <c r="V758" s="5">
+      <c r="V758">
         <v>2.68</v>
       </c>
-      <c r="W758" s="5">
-        <v>0</v>
-      </c>
-      <c r="X758" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="759" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W758">
+        <v>0</v>
+      </c>
+      <c r="X758" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="759" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>803</v>
       </c>
       <c r="B759">
         <v>3</v>
       </c>
-      <c r="C759" s="3">
+      <c r="C759">
         <v>7</v>
       </c>
-      <c r="D759" s="4">
+      <c r="D759">
         <v>1.9333333333333329</v>
       </c>
-      <c r="E759" s="5" t="b">
+      <c r="E759" t="b">
         <v>0</v>
       </c>
       <c r="F759">
@@ -59774,146 +59777,146 @@
       <c r="G759" s="2" t="s">
         <v>829</v>
       </c>
-      <c r="H759" s="5">
+      <c r="H759">
         <v>475</v>
       </c>
-      <c r="I759" s="5">
+      <c r="I759">
         <v>487</v>
       </c>
       <c r="J759" s="2" t="s">
         <v>830</v>
       </c>
-      <c r="K759" s="5">
+      <c r="K759">
         <v>6.8669355220765699E-2</v>
       </c>
-      <c r="L759" s="5">
+      <c r="L759">
         <v>0.77</v>
       </c>
-      <c r="M759" s="5">
+      <c r="M759">
         <v>2.1</v>
       </c>
-      <c r="N759" s="5">
+      <c r="N759">
         <v>1.33</v>
       </c>
-      <c r="O759" s="5">
+      <c r="O759">
         <v>1.04</v>
       </c>
-      <c r="P759" s="5">
+      <c r="P759">
         <v>1.67</v>
       </c>
-      <c r="Q759" s="5">
+      <c r="Q759">
         <v>1.04</v>
       </c>
-      <c r="R759" s="5">
+      <c r="R759">
         <v>1.17</v>
       </c>
-      <c r="S759" s="5">
+      <c r="S759">
         <v>2.64</v>
       </c>
-      <c r="T759" s="5">
+      <c r="T759">
         <v>1.77</v>
       </c>
-      <c r="U759" s="5">
+      <c r="U759">
         <v>2.36</v>
       </c>
-      <c r="V759" s="5">
+      <c r="V759">
         <v>1.25</v>
       </c>
-      <c r="W759" s="5">
-        <v>0</v>
-      </c>
-      <c r="X759" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="760" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W759">
+        <v>0</v>
+      </c>
+      <c r="X759" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>804</v>
       </c>
       <c r="B760">
         <v>3</v>
       </c>
-      <c r="C760" s="3">
+      <c r="C760">
         <v>8</v>
       </c>
-      <c r="D760" s="4">
+      <c r="D760">
         <v>6.6666666666666763E-2</v>
       </c>
-      <c r="E760" s="5" t="b">
+      <c r="E760" t="b">
         <v>0</v>
       </c>
       <c r="F760">
         <v>0.13361415266990601</v>
       </c>
-      <c r="G760" s="5">
+      <c r="G760">
         <v>0.98044009779951102</v>
       </c>
-      <c r="H760" s="5">
+      <c r="H760">
         <v>401</v>
       </c>
-      <c r="I760" s="5">
+      <c r="I760">
         <v>409</v>
       </c>
       <c r="J760" s="2" t="s">
         <v>831</v>
       </c>
-      <c r="K760" s="5">
+      <c r="K760">
         <v>5.5857741467011598E-2</v>
       </c>
-      <c r="L760" s="5">
+      <c r="L760">
         <v>0.77</v>
       </c>
-      <c r="M760" s="5">
+      <c r="M760">
         <v>1.22</v>
       </c>
-      <c r="N760" s="5">
+      <c r="N760">
         <v>0.16</v>
       </c>
-      <c r="O760" s="5">
+      <c r="O760">
         <v>0.12</v>
       </c>
-      <c r="P760" s="5">
+      <c r="P760">
         <v>1.04</v>
       </c>
-      <c r="Q760" s="5">
+      <c r="Q760">
         <v>0.03</v>
       </c>
-      <c r="R760" s="5">
+      <c r="R760">
         <v>0.32</v>
       </c>
-      <c r="S760" s="5">
+      <c r="S760">
         <v>1.96</v>
       </c>
-      <c r="T760" s="5">
+      <c r="T760">
         <v>0.77</v>
       </c>
-      <c r="U760" s="5">
+      <c r="U760">
         <v>1.63</v>
       </c>
-      <c r="V760" s="5">
+      <c r="V760">
         <v>1.95</v>
       </c>
-      <c r="W760" s="5">
-        <v>0</v>
-      </c>
-      <c r="X760" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="761" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W760">
+        <v>0</v>
+      </c>
+      <c r="X760" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="761" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>805</v>
       </c>
       <c r="B761">
         <v>3</v>
       </c>
-      <c r="C761" s="3">
+      <c r="C761">
         <v>8</v>
       </c>
-      <c r="D761" s="4">
+      <c r="D761">
         <v>-0.1333333333333333</v>
       </c>
-      <c r="E761" s="5" t="b">
+      <c r="E761" t="b">
         <v>0</v>
       </c>
       <c r="F761">
@@ -59922,84 +59925,84 @@
       <c r="G761" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="H761" s="5">
+      <c r="H761">
         <v>663</v>
       </c>
-      <c r="I761" s="5">
+      <c r="I761">
         <v>665</v>
       </c>
       <c r="J761" s="2" t="s">
         <v>833</v>
       </c>
-      <c r="K761" s="5">
+      <c r="K761">
         <v>4.7720380981021798E-2</v>
       </c>
-      <c r="L761" s="5">
+      <c r="L761">
         <v>0.77</v>
       </c>
-      <c r="M761" s="5">
+      <c r="M761">
         <v>0.77</v>
       </c>
-      <c r="N761" s="5">
+      <c r="N761">
         <v>0.74</v>
       </c>
-      <c r="O761" s="5">
+      <c r="O761">
         <v>0.8</v>
       </c>
-      <c r="P761" s="5">
+      <c r="P761">
         <v>0.56999999999999995</v>
       </c>
-      <c r="Q761" s="5">
+      <c r="Q761">
         <v>0.98</v>
       </c>
-      <c r="R761" s="5">
+      <c r="R761">
         <v>0.89</v>
       </c>
-      <c r="S761" s="5">
+      <c r="S761">
         <v>1.92</v>
       </c>
-      <c r="T761" s="5">
+      <c r="T761">
         <v>0.99</v>
       </c>
-      <c r="U761" s="5">
+      <c r="U761">
         <v>1.69</v>
       </c>
-      <c r="V761" s="5">
+      <c r="V761">
         <v>1.41</v>
       </c>
-      <c r="W761" s="5">
-        <v>0</v>
-      </c>
-      <c r="X761" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="762" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W761">
+        <v>0</v>
+      </c>
+      <c r="X761" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>806</v>
       </c>
       <c r="B762">
         <v>3</v>
       </c>
-      <c r="C762" s="3">
+      <c r="C762">
         <v>8</v>
       </c>
-      <c r="D762" s="4">
-        <v>0</v>
-      </c>
-      <c r="E762" s="5" t="b">
+      <c r="D762">
+        <v>0</v>
+      </c>
+      <c r="E762" t="b">
         <v>0</v>
       </c>
       <c r="F762">
         <v>0.14687116444110801</v>
       </c>
-      <c r="G762" s="5">
+      <c r="G762">
         <v>0.634020618556701</v>
       </c>
-      <c r="H762" s="5">
+      <c r="H762">
         <v>246</v>
       </c>
-      <c r="I762" s="5">
+      <c r="I762">
         <v>388</v>
       </c>
       <c r="J762" s="2" t="s">
@@ -60008,134 +60011,134 @@
       <c r="K762" s="2" t="s">
         <v>835</v>
       </c>
-      <c r="L762" s="5">
+      <c r="L762">
         <v>0.77</v>
       </c>
-      <c r="M762" s="5">
+      <c r="M762">
         <v>3.02</v>
       </c>
-      <c r="N762" s="5">
+      <c r="N762">
         <v>0.36</v>
       </c>
-      <c r="O762" s="5">
+      <c r="O762">
         <v>2.14</v>
       </c>
-      <c r="P762" s="5">
+      <c r="P762">
         <v>1.1299999999999999</v>
       </c>
-      <c r="Q762" s="5">
+      <c r="Q762">
         <v>1.81</v>
       </c>
-      <c r="R762" s="5">
+      <c r="R762">
         <v>1.1100000000000001</v>
       </c>
-      <c r="S762" s="5">
+      <c r="S762">
         <v>3.24</v>
       </c>
-      <c r="T762" s="5">
+      <c r="T762">
         <v>5</v>
       </c>
-      <c r="U762" s="5">
+      <c r="U762">
         <v>2.48</v>
       </c>
-      <c r="V762" s="5">
+      <c r="V762">
         <v>1.91</v>
       </c>
-      <c r="W762" s="5">
+      <c r="W762">
         <v>2</v>
       </c>
-      <c r="X762" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="763" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="X762" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="763" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>807</v>
       </c>
       <c r="B763">
         <v>3</v>
       </c>
-      <c r="C763" s="3">
+      <c r="C763">
         <v>5</v>
       </c>
-      <c r="D763" s="4">
+      <c r="D763">
         <v>-3.3333333333333333E-2</v>
       </c>
-      <c r="E763" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F763" s="5">
+      <c r="E763" t="b">
+        <v>0</v>
+      </c>
+      <c r="F763">
         <v>0.29985560950907741</v>
       </c>
-      <c r="G763" s="5">
+      <c r="G763">
         <v>0.82439024390243898</v>
       </c>
-      <c r="H763" s="5">
+      <c r="H763">
         <v>169</v>
       </c>
-      <c r="I763" s="5">
+      <c r="I763">
         <v>205</v>
       </c>
       <c r="J763" s="2" t="s">
         <v>836</v>
       </c>
-      <c r="K763" s="5">
+      <c r="K763">
         <v>7.4437829225714E-2</v>
       </c>
-      <c r="L763" s="5">
+      <c r="L763">
         <v>0.77</v>
       </c>
-      <c r="M763" s="5">
+      <c r="M763">
         <v>1.7</v>
       </c>
-      <c r="N763" s="5">
+      <c r="N763">
         <v>0.47</v>
       </c>
-      <c r="O763" s="5">
+      <c r="O763">
         <v>0.28000000000000003</v>
       </c>
-      <c r="P763" s="5">
+      <c r="P763">
         <v>1.92</v>
       </c>
-      <c r="Q763" s="5">
+      <c r="Q763">
         <v>1.83</v>
       </c>
-      <c r="R763" s="5">
+      <c r="R763">
         <v>0.7</v>
       </c>
-      <c r="S763" s="5">
+      <c r="S763">
         <v>2.04</v>
       </c>
-      <c r="T763" s="5">
+      <c r="T763">
         <v>0.93</v>
       </c>
-      <c r="U763" s="5">
+      <c r="U763">
         <v>2.2000000000000002</v>
       </c>
-      <c r="V763" s="5">
+      <c r="V763">
         <v>1.77</v>
       </c>
-      <c r="W763" s="5">
-        <v>0</v>
-      </c>
-      <c r="X763" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="764" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W763">
+        <v>0</v>
+      </c>
+      <c r="X763" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="764" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>808</v>
       </c>
       <c r="B764">
         <v>3</v>
       </c>
-      <c r="C764" s="3">
+      <c r="C764">
         <v>7</v>
       </c>
-      <c r="D764" s="4">
+      <c r="D764">
         <v>-9.9999999999999978E-2</v>
       </c>
-      <c r="E764" s="5" t="b">
+      <c r="E764" t="b">
         <v>0</v>
       </c>
       <c r="F764">
@@ -60144,72 +60147,72 @@
       <c r="G764" s="2" t="s">
         <v>837</v>
       </c>
-      <c r="H764" s="5">
+      <c r="H764">
         <v>115</v>
       </c>
-      <c r="I764" s="5">
+      <c r="I764">
         <v>296</v>
       </c>
-      <c r="J764" s="5">
+      <c r="J764">
         <v>0.97043478260869598</v>
       </c>
-      <c r="K764" s="5">
+      <c r="K764">
         <v>4.3172264170329003E-2</v>
       </c>
-      <c r="L764" s="5">
+      <c r="L764">
         <v>0.77</v>
       </c>
-      <c r="M764" s="5">
+      <c r="M764">
         <v>2.5299999999999998</v>
       </c>
-      <c r="N764" s="5">
+      <c r="N764">
         <v>0.78</v>
       </c>
-      <c r="O764" s="5">
+      <c r="O764">
         <v>2.2200000000000002</v>
       </c>
-      <c r="P764" s="5">
+      <c r="P764">
         <v>0.82</v>
       </c>
-      <c r="Q764" s="5">
+      <c r="Q764">
         <v>1.8</v>
       </c>
-      <c r="R764" s="5">
+      <c r="R764">
         <v>0.78</v>
       </c>
-      <c r="S764" s="5">
+      <c r="S764">
         <v>3.35</v>
       </c>
-      <c r="T764" s="5">
+      <c r="T764">
         <v>1.98</v>
       </c>
-      <c r="U764" s="5">
+      <c r="U764">
         <v>1.74</v>
       </c>
-      <c r="V764" s="5">
+      <c r="V764">
         <v>2.58</v>
       </c>
-      <c r="W764" s="5">
+      <c r="W764">
         <v>1</v>
       </c>
-      <c r="X764" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="765" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="X764" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="765" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>809</v>
       </c>
       <c r="B765">
         <v>3</v>
       </c>
-      <c r="C765" s="3">
+      <c r="C765">
         <v>10</v>
       </c>
-      <c r="D765" s="4">
+      <c r="D765">
         <v>3.3333333333333333E-2</v>
       </c>
-      <c r="E765" s="5" t="b">
+      <c r="E765" t="b">
         <v>0</v>
       </c>
       <c r="F765">
@@ -60218,72 +60221,72 @@
       <c r="G765" s="2" t="s">
         <v>838</v>
       </c>
-      <c r="H765" s="5">
+      <c r="H765">
         <v>403</v>
       </c>
-      <c r="I765" s="5">
+      <c r="I765">
         <v>441</v>
       </c>
       <c r="J765" s="2" t="s">
         <v>839</v>
       </c>
-      <c r="K765" s="5">
+      <c r="K765">
         <v>7.9417452959808496E-2</v>
       </c>
-      <c r="L765" s="5">
+      <c r="L765">
         <v>0.77</v>
       </c>
-      <c r="M765" s="5">
+      <c r="M765">
         <v>0.56000000000000005</v>
       </c>
-      <c r="N765" s="5">
+      <c r="N765">
         <v>0.55000000000000004</v>
       </c>
-      <c r="O765" s="5">
+      <c r="O765">
         <v>0.35</v>
       </c>
-      <c r="P765" s="5">
+      <c r="P765">
         <v>2.16</v>
       </c>
-      <c r="Q765" s="5">
+      <c r="Q765">
         <v>0.9</v>
       </c>
-      <c r="R765" s="5">
+      <c r="R765">
         <v>0.53</v>
       </c>
-      <c r="S765" s="5">
+      <c r="S765">
         <v>2.61</v>
       </c>
-      <c r="T765" s="5">
+      <c r="T765">
         <v>1.1200000000000001</v>
       </c>
-      <c r="U765" s="5">
+      <c r="U765">
         <v>1.91</v>
       </c>
-      <c r="V765" s="5">
+      <c r="V765">
         <v>1.55</v>
       </c>
-      <c r="W765" s="5">
-        <v>0</v>
-      </c>
-      <c r="X765" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="766" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W765">
+        <v>0</v>
+      </c>
+      <c r="X765" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="766" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>810</v>
       </c>
       <c r="B766">
         <v>3</v>
       </c>
-      <c r="C766" s="3">
+      <c r="C766">
         <v>6</v>
       </c>
-      <c r="D766" s="4">
+      <c r="D766">
         <v>-3.3333333333333333E-2</v>
       </c>
-      <c r="E766" s="5" t="b">
+      <c r="E766" t="b">
         <v>0</v>
       </c>
       <c r="F766">
@@ -60292,72 +60295,72 @@
       <c r="G766" s="2" t="s">
         <v>840</v>
       </c>
-      <c r="H766" s="5">
+      <c r="H766">
         <v>139</v>
       </c>
-      <c r="I766" s="5">
+      <c r="I766">
         <v>252</v>
       </c>
-      <c r="J766" s="5">
+      <c r="J766">
         <v>0.91776978417266197</v>
       </c>
-      <c r="K766" s="5">
+      <c r="K766">
         <v>6.7308969248216999E-2</v>
       </c>
-      <c r="L766" s="5">
+      <c r="L766">
         <v>0.77</v>
       </c>
-      <c r="M766" s="5">
+      <c r="M766">
         <v>2.75</v>
       </c>
-      <c r="N766" s="5">
+      <c r="N766">
         <v>0.8</v>
       </c>
-      <c r="O766" s="5">
+      <c r="O766">
         <v>1.22</v>
       </c>
-      <c r="P766" s="5">
+      <c r="P766">
         <v>1.33</v>
       </c>
-      <c r="Q766" s="5">
+      <c r="Q766">
         <v>2.17</v>
       </c>
-      <c r="R766" s="5">
+      <c r="R766">
         <v>0.98</v>
       </c>
-      <c r="S766" s="5">
+      <c r="S766">
         <v>4.79</v>
       </c>
-      <c r="T766" s="5">
+      <c r="T766">
         <v>1.94</v>
       </c>
-      <c r="U766" s="5">
+      <c r="U766">
         <v>2.21</v>
       </c>
-      <c r="V766" s="5">
+      <c r="V766">
         <v>2.59</v>
       </c>
-      <c r="W766" s="5">
+      <c r="W766">
         <v>2</v>
       </c>
-      <c r="X766" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="767" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="X766" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="767" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>811</v>
       </c>
       <c r="B767">
         <v>3</v>
       </c>
-      <c r="C767" s="3">
+      <c r="C767">
         <v>10</v>
       </c>
-      <c r="D767" s="4">
+      <c r="D767">
         <v>3.3333333333333437E-2</v>
       </c>
-      <c r="E767" s="5" t="b">
+      <c r="E767" t="b">
         <v>0</v>
       </c>
       <c r="F767">
@@ -60366,72 +60369,72 @@
       <c r="G767" s="2" t="s">
         <v>841</v>
       </c>
-      <c r="H767" s="5">
+      <c r="H767">
         <v>284</v>
       </c>
-      <c r="I767" s="5">
+      <c r="I767">
         <v>520</v>
       </c>
       <c r="J767" s="2" t="s">
         <v>842</v>
       </c>
-      <c r="K767" s="5">
+      <c r="K767">
         <v>6.9083294778685203E-2</v>
       </c>
-      <c r="L767" s="5">
+      <c r="L767">
         <v>0.77</v>
       </c>
-      <c r="M767" s="5">
+      <c r="M767">
         <v>2.13</v>
       </c>
-      <c r="N767" s="5">
+      <c r="N767">
         <v>0.82</v>
       </c>
-      <c r="O767" s="5">
+      <c r="O767">
         <v>1.73</v>
       </c>
-      <c r="P767" s="5">
+      <c r="P767">
         <v>0.87</v>
       </c>
-      <c r="Q767" s="5">
+      <c r="Q767">
         <v>1.1499999999999999</v>
       </c>
-      <c r="R767" s="5">
+      <c r="R767">
         <v>0.93</v>
       </c>
-      <c r="S767" s="5">
+      <c r="S767">
         <v>2.75</v>
       </c>
-      <c r="T767" s="5">
+      <c r="T767">
         <v>1.97</v>
       </c>
-      <c r="U767" s="5">
+      <c r="U767">
         <v>3.18</v>
       </c>
-      <c r="V767" s="5">
+      <c r="V767">
         <v>3.11</v>
       </c>
-      <c r="W767" s="5">
-        <v>0</v>
-      </c>
-      <c r="X767" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="768" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="W767">
+        <v>0</v>
+      </c>
+      <c r="X767" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="768" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>812</v>
       </c>
       <c r="B768">
         <v>3</v>
       </c>
-      <c r="C768" s="3">
+      <c r="C768">
         <v>10</v>
       </c>
-      <c r="D768" s="4">
-        <v>0</v>
-      </c>
-      <c r="E768" s="5" t="b">
+      <c r="D768">
+        <v>0</v>
+      </c>
+      <c r="E768" t="b">
         <v>0</v>
       </c>
       <c r="F768">
@@ -60440,72 +60443,72 @@
       <c r="G768" s="2" t="s">
         <v>843</v>
       </c>
-      <c r="H768" s="5">
+      <c r="H768">
         <v>316</v>
       </c>
-      <c r="I768" s="5">
+      <c r="I768">
         <v>498</v>
       </c>
       <c r="J768" s="2" t="s">
         <v>844</v>
       </c>
-      <c r="K768" s="5">
+      <c r="K768">
         <v>7.3193329010872193E-2</v>
       </c>
-      <c r="L768" s="5">
+      <c r="L768">
         <v>0.77</v>
       </c>
-      <c r="M768" s="5">
+      <c r="M768">
         <v>2.2599999999999998</v>
       </c>
-      <c r="N768" s="5">
+      <c r="N768">
         <v>2.27</v>
       </c>
-      <c r="O768" s="5">
+      <c r="O768">
         <v>2.2400000000000002</v>
       </c>
-      <c r="P768" s="5">
+      <c r="P768">
         <v>1.61</v>
       </c>
-      <c r="Q768" s="5">
+      <c r="Q768">
         <v>1.9</v>
       </c>
-      <c r="R768" s="5">
+      <c r="R768">
         <v>2.4900000000000002</v>
       </c>
-      <c r="S768" s="5">
+      <c r="S768">
         <v>1.67</v>
       </c>
-      <c r="T768" s="5">
+      <c r="T768">
         <v>2.2599999999999998</v>
       </c>
-      <c r="U768" s="5">
+      <c r="U768">
         <v>1.96</v>
       </c>
-      <c r="V768" s="5">
+      <c r="V768">
         <v>1.86</v>
       </c>
-      <c r="W768" s="5">
-        <v>0</v>
-      </c>
-      <c r="X768" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="769" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W768">
+        <v>0</v>
+      </c>
+      <c r="X768" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="769" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>813</v>
       </c>
       <c r="B769">
         <v>3</v>
       </c>
-      <c r="C769" s="3">
+      <c r="C769">
         <v>5</v>
       </c>
-      <c r="D769" s="4">
+      <c r="D769">
         <v>0.33333333333333343</v>
       </c>
-      <c r="E769" s="5" t="b">
+      <c r="E769" t="b">
         <v>0</v>
       </c>
       <c r="F769">
@@ -60514,146 +60517,146 @@
       <c r="G769" s="2" t="s">
         <v>845</v>
       </c>
-      <c r="H769" s="5">
+      <c r="H769">
         <v>168</v>
       </c>
-      <c r="I769" s="5">
+      <c r="I769">
         <v>302</v>
       </c>
       <c r="J769" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="K769" s="5">
+      <c r="K769">
         <v>7.6259853776252898E-2</v>
       </c>
-      <c r="L769" s="5">
+      <c r="L769">
         <v>0.77</v>
       </c>
-      <c r="M769" s="5">
+      <c r="M769">
         <v>1.77</v>
       </c>
-      <c r="N769" s="5">
+      <c r="N769">
         <v>0.57999999999999996</v>
       </c>
-      <c r="O769" s="5">
+      <c r="O769">
         <v>1.55</v>
       </c>
-      <c r="P769" s="5">
+      <c r="P769">
         <v>0.81</v>
       </c>
-      <c r="Q769" s="5">
+      <c r="Q769">
         <v>1.61</v>
       </c>
-      <c r="R769" s="5">
+      <c r="R769">
         <v>0.65</v>
       </c>
-      <c r="S769" s="5">
+      <c r="S769">
         <v>1.83</v>
       </c>
-      <c r="T769" s="5">
+      <c r="T769">
         <v>1.77</v>
       </c>
-      <c r="U769" s="5">
+      <c r="U769">
         <v>2.3199999999999998</v>
       </c>
-      <c r="V769" s="5">
+      <c r="V769">
         <v>1.78</v>
       </c>
-      <c r="W769" s="5">
-        <v>0</v>
-      </c>
-      <c r="X769" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="770" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W769">
+        <v>0</v>
+      </c>
+      <c r="X769" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="770" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>814</v>
       </c>
       <c r="B770">
         <v>3</v>
       </c>
-      <c r="C770" s="3">
+      <c r="C770">
         <v>4</v>
       </c>
-      <c r="D770" s="4">
+      <c r="D770">
         <v>-3.3333333333333333E-2</v>
       </c>
-      <c r="E770" s="5" t="b">
+      <c r="E770" t="b">
         <v>0</v>
       </c>
       <c r="F770">
         <v>0.29985560950907741</v>
       </c>
-      <c r="G770" s="5">
+      <c r="G770">
         <v>0.97402597402597402</v>
       </c>
-      <c r="H770" s="5">
+      <c r="H770">
         <v>225</v>
       </c>
-      <c r="I770" s="5">
+      <c r="I770">
         <v>231</v>
       </c>
       <c r="J770" s="2" t="s">
         <v>847</v>
       </c>
-      <c r="K770" s="5">
+      <c r="K770">
         <v>6.4842605531112693E-2</v>
       </c>
-      <c r="L770" s="5">
+      <c r="L770">
         <v>0.77</v>
       </c>
-      <c r="M770" s="5">
+      <c r="M770">
         <v>0.97</v>
       </c>
-      <c r="N770" s="5">
+      <c r="N770">
         <v>1.22</v>
       </c>
-      <c r="O770" s="5">
+      <c r="O770">
         <v>0.92</v>
       </c>
-      <c r="P770" s="5">
+      <c r="P770">
         <v>1.03</v>
       </c>
-      <c r="Q770" s="5">
+      <c r="Q770">
         <v>1.5</v>
       </c>
-      <c r="R770" s="5">
+      <c r="R770">
         <v>1.7</v>
       </c>
-      <c r="S770" s="5">
+      <c r="S770">
         <v>4.1500000000000004</v>
       </c>
-      <c r="T770" s="5">
+      <c r="T770">
         <v>1.69</v>
       </c>
-      <c r="U770" s="5">
+      <c r="U770">
         <v>1.5</v>
       </c>
-      <c r="V770" s="5">
+      <c r="V770">
         <v>2.69</v>
       </c>
-      <c r="W770" s="5">
-        <v>0</v>
-      </c>
-      <c r="X770" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="771" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="W770">
+        <v>0</v>
+      </c>
+      <c r="X770" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="771" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>815</v>
       </c>
       <c r="B771">
         <v>3</v>
       </c>
-      <c r="C771" s="3">
+      <c r="C771">
         <v>5</v>
       </c>
-      <c r="D771" s="4">
+      <c r="D771">
         <v>0.20000000000000009</v>
       </c>
-      <c r="E771" s="5" t="b">
+      <c r="E771" t="b">
         <v>0</v>
       </c>
       <c r="F771">
@@ -60662,72 +60665,72 @@
       <c r="G771" s="2" t="s">
         <v>848</v>
       </c>
-      <c r="H771" s="5">
+      <c r="H771">
         <v>108</v>
       </c>
-      <c r="I771" s="5">
+      <c r="I771">
         <v>246</v>
       </c>
       <c r="J771" s="2" t="s">
         <v>849</v>
       </c>
-      <c r="K771" s="5">
+      <c r="K771">
         <v>6.6901973101291701E-2</v>
       </c>
-      <c r="L771" s="5">
+      <c r="L771">
         <v>0.77</v>
       </c>
-      <c r="M771" s="5">
+      <c r="M771">
         <v>2.25</v>
       </c>
-      <c r="N771" s="5">
+      <c r="N771">
         <v>0.74</v>
       </c>
-      <c r="O771" s="5">
+      <c r="O771">
         <v>1.74</v>
       </c>
-      <c r="P771" s="5">
+      <c r="P771">
         <v>2.5299999999999998</v>
       </c>
-      <c r="Q771" s="5">
+      <c r="Q771">
         <v>1.1599999999999999</v>
       </c>
-      <c r="R771" s="5">
+      <c r="R771">
         <v>0.81</v>
       </c>
-      <c r="S771" s="5">
+      <c r="S771">
         <v>1.71</v>
       </c>
-      <c r="T771" s="5">
+      <c r="T771">
         <v>0.6</v>
       </c>
-      <c r="U771" s="5">
+      <c r="U771">
         <v>1.36</v>
       </c>
-      <c r="V771" s="5">
+      <c r="V771">
         <v>2.3199999999999998</v>
       </c>
-      <c r="W771" s="5">
+      <c r="W771">
         <v>1</v>
       </c>
-      <c r="X771" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="772" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="X771" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="772" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>816</v>
       </c>
       <c r="B772">
         <v>3</v>
       </c>
-      <c r="C772" s="3">
+      <c r="C772">
         <v>10</v>
       </c>
-      <c r="D772" s="4">
+      <c r="D772">
         <v>6.6666666666666652E-2</v>
       </c>
-      <c r="E772" s="5" t="b">
+      <c r="E772" t="b">
         <v>0</v>
       </c>
       <c r="F772">
@@ -60736,72 +60739,72 @@
       <c r="G772" s="2" t="s">
         <v>850</v>
       </c>
-      <c r="H772" s="5">
+      <c r="H772">
         <v>228</v>
       </c>
-      <c r="I772" s="5">
+      <c r="I772">
         <v>523</v>
       </c>
       <c r="J772" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="K772" s="5">
+      <c r="K772">
         <v>4.9848580521244502E-2</v>
       </c>
-      <c r="L772" s="5">
+      <c r="L772">
         <v>0.77</v>
       </c>
-      <c r="M772" s="5">
+      <c r="M772">
         <v>3.3</v>
       </c>
-      <c r="N772" s="5">
+      <c r="N772">
         <v>0.28999999999999998</v>
       </c>
-      <c r="O772" s="5">
+      <c r="O772">
         <v>1.63</v>
       </c>
-      <c r="P772" s="5">
+      <c r="P772">
         <v>2.57</v>
       </c>
-      <c r="Q772" s="5">
+      <c r="Q772">
         <v>1.36</v>
       </c>
-      <c r="R772" s="5">
+      <c r="R772">
         <v>0.56000000000000005</v>
       </c>
-      <c r="S772" s="5">
+      <c r="S772">
         <v>3.66</v>
       </c>
-      <c r="T772" s="5">
+      <c r="T772">
         <v>5</v>
       </c>
-      <c r="U772" s="5">
+      <c r="U772">
         <v>2.1</v>
       </c>
-      <c r="V772" s="5">
+      <c r="V772">
         <v>5</v>
       </c>
-      <c r="W772" s="5">
+      <c r="W772">
         <v>2</v>
       </c>
-      <c r="X772" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="773" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="X772" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="773" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>817</v>
       </c>
       <c r="B773">
         <v>3</v>
       </c>
-      <c r="C773" s="3">
+      <c r="C773">
         <v>6</v>
       </c>
-      <c r="D773" s="4">
+      <c r="D773">
         <v>-0.13333333333333339</v>
       </c>
-      <c r="E773" s="5" t="b">
+      <c r="E773" t="b">
         <v>0</v>
       </c>
       <c r="F773">
@@ -60810,10 +60813,10 @@
       <c r="G773" s="2" t="s">
         <v>852</v>
       </c>
-      <c r="H773" s="5">
+      <c r="H773">
         <v>134</v>
       </c>
-      <c r="I773" s="5">
+      <c r="I773">
         <v>308</v>
       </c>
       <c r="J773" s="2" t="s">
@@ -60822,60 +60825,60 @@
       <c r="K773" s="2" t="s">
         <v>854</v>
       </c>
-      <c r="L773" s="5">
+      <c r="L773">
         <v>0.77</v>
       </c>
-      <c r="M773" s="5">
+      <c r="M773">
         <v>3.28</v>
       </c>
-      <c r="N773" s="5">
+      <c r="N773">
         <v>0.42</v>
       </c>
-      <c r="O773" s="5">
+      <c r="O773">
         <v>1.38</v>
       </c>
-      <c r="P773" s="5">
+      <c r="P773">
         <v>1.46</v>
       </c>
-      <c r="Q773" s="5">
+      <c r="Q773">
         <v>1.42</v>
       </c>
-      <c r="R773" s="5">
+      <c r="R773">
         <v>0.53</v>
       </c>
-      <c r="S773" s="5">
+      <c r="S773">
         <v>3.77</v>
       </c>
-      <c r="T773" s="5">
+      <c r="T773">
         <v>4.82</v>
       </c>
-      <c r="U773" s="5">
+      <c r="U773">
         <v>1.44</v>
       </c>
-      <c r="V773" s="5">
+      <c r="V773">
         <v>2.23</v>
       </c>
-      <c r="W773" s="5">
+      <c r="W773">
         <v>2</v>
       </c>
-      <c r="X773" s="5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="774" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="X773" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="774" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>818</v>
       </c>
       <c r="B774">
         <v>3</v>
       </c>
-      <c r="C774" s="3">
+      <c r="C774">
         <v>6</v>
       </c>
-      <c r="D774" s="4">
+      <c r="D774">
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="E774" s="5" t="b">
+      <c r="E774" t="b">
         <v>0</v>
       </c>
       <c r="F774">
@@ -60884,55 +60887,55 @@
       <c r="G774" s="2" t="s">
         <v>855</v>
       </c>
-      <c r="H774" s="5">
+      <c r="H774">
         <v>189</v>
       </c>
-      <c r="I774" s="5">
+      <c r="I774">
         <v>309</v>
       </c>
       <c r="J774" s="2" t="s">
         <v>856</v>
       </c>
-      <c r="K774" s="5">
+      <c r="K774">
         <v>6.2485571902128299E-2</v>
       </c>
-      <c r="L774" s="5">
+      <c r="L774">
         <v>0.77</v>
       </c>
-      <c r="M774" s="5">
+      <c r="M774">
         <v>2.86</v>
       </c>
-      <c r="N774" s="5">
+      <c r="N774">
         <v>0.31</v>
       </c>
-      <c r="O774" s="5">
+      <c r="O774">
         <v>1.89</v>
       </c>
-      <c r="P774" s="5">
+      <c r="P774">
         <v>0.95</v>
       </c>
-      <c r="Q774" s="5">
+      <c r="Q774">
         <v>1.08</v>
       </c>
-      <c r="R774" s="5">
+      <c r="R774">
         <v>1.21</v>
       </c>
-      <c r="S774" s="5">
+      <c r="S774">
         <v>1.92</v>
       </c>
-      <c r="T774" s="5">
+      <c r="T774">
         <v>1.41</v>
       </c>
-      <c r="U774" s="5">
+      <c r="U774">
         <v>1.88</v>
       </c>
-      <c r="V774" s="5">
+      <c r="V774">
         <v>2.11</v>
       </c>
-      <c r="W774" s="5">
+      <c r="W774">
         <v>1</v>
       </c>
-      <c r="X774" s="5" t="b">
+      <c r="X774" t="b">
         <v>0</v>
       </c>
     </row>
